--- a/Tableau_de_synthese_Ryan_Hadjout.xlsx
+++ b/Tableau_de_synthese_Ryan_Hadjout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ryan94\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CABCB7C-075D-46B5-8032-A41081DB90A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E472FB9-F31E-4999-87E1-3C62C5A24835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26460" yWindow="2085" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28545" yWindow="2760" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -113,54 +113,22 @@
 </t>
   </si>
   <si>
-    <t>Création d'un site Web (HTML, CSS, SSL)
-Documents : Rapport de TP, captures d'écran du site, certificat SSL</t>
-  </si>
-  <si>
     <t>09/2023 au 12/2023</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
-    <t>Projet Cleanergy : Mise en place d'un AD, une base de données et un serveur WEB
-Documents : Rapport de projet, schéma réseau, captures d'écran AD et serveur WEB</t>
-  </si>
-  <si>
     <t>10/09/24 au 10/12/24</t>
-  </si>
-  <si>
-    <t>Sécurisation de l'Active Directory et de Windows Server
-Documents : Rapport d'audit Purple Knight (avant/après), captures HardeningKitty</t>
-  </si>
-  <si>
-    <t>TP mise en place d'un serveur GLPI
-Documents : Procédure d'installation GLPI (PDF), captures d'écran, fichier Gantt</t>
-  </si>
-  <si>
-    <t>Installation et configuration de Zabbix sur Ubuntu (architecture client-serveur)
-Documents : Tutoriel complet (15 pages), captures d'écran supervision réseau, alertes email configurées, dashboard Zabbix</t>
   </si>
   <si>
     <t>11/03/25 au 25/03/25</t>
   </si>
   <si>
-    <t>Portfolio
-Documents : Site portfolio en ligne (ryan94dz1.github.io/portfolio), CV PDF</t>
-  </si>
-  <si>
     <t>02/03/25 au 28/03/25</t>
   </si>
   <si>
-    <t>TP Stormshield
-Documents : Rapport de configuration, règles de filtrage, schéma réseau</t>
-  </si>
-  <si>
     <t>03/03/25 au 28/03/25</t>
-  </si>
-  <si>
-    <t>Sécurisation HTTPS avec ADCS (PKI d'entreprise)
-Documents : Tutoriel ADCS complet (PDF), certificat exporté, configuration Apache</t>
   </si>
   <si>
     <t>01/03/26 au 18/03/26</t>
@@ -169,39 +137,58 @@
     <t>Réalisations en milieu professionnel en cours de première année</t>
   </si>
   <si>
-    <t>Traitement des tickets sur GLPI (Stage 1ère année)
-Documents : Rapport de stage, exemples de tickets traités</t>
-  </si>
-  <si>
     <t>27/05/24 au 05/07/24</t>
-  </si>
-  <si>
-    <t>Matérisation des postes, configurations des téléphones Cisco
-Documents : Rapport de stage, procédure de déploiement</t>
   </si>
   <si>
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t>Mise en place d'un HoneyPot
-Documents : Rapport technique, captures d'écran des alertes détectées</t>
-  </si>
-  <si>
     <t>06/01/25 au 14/02/25</t>
-  </si>
-  <si>
-    <t>Traitement des tickets sur GLPI (Stage 2ème année)
-Documents : Rapport de stage, tableau de suivi des incidents</t>
-  </si>
-  <si>
-    <t>Création et installation WSUS
-Documents : Procédure d'installation WSUS (PDF), captures d'écran, GPO configurées</t>
   </si>
   <si>
     <t>19/01/26 au 31/01/26</t>
   </si>
   <si>
     <t>Adresse URL du portfolio : https://ryan-hadjout.github.io/portfolio/</t>
+  </si>
+  <si>
+    <t>Projet Cleanergy : Mise en place d'un AD, une base de données et un serveur WEB</t>
+  </si>
+  <si>
+    <t>Création d'un site Web (HTML, CSS, SSL)</t>
+  </si>
+  <si>
+    <t>Sécurisation de l'Active Directory et de Windows Server</t>
+  </si>
+  <si>
+    <t>TP mise en place d'un serveur GLPI</t>
+  </si>
+  <si>
+    <t>Installation et configuration de Zabbix sur Ubuntu</t>
+  </si>
+  <si>
+    <t>Portfolio</t>
+  </si>
+  <si>
+    <t>TP Stormshield</t>
+  </si>
+  <si>
+    <t>Sécurisation HTTPS avec ADCS (PKI d'entreprise)</t>
+  </si>
+  <si>
+    <t>Traitement des tickets sur GLPI (Stage 1ère année)</t>
+  </si>
+  <si>
+    <t>Matérisation des postes, configurations des téléphones Cisco</t>
+  </si>
+  <si>
+    <t>Mise en place d'un HoneyPot</t>
+  </si>
+  <si>
+    <t>Traitement des tickets sur GLPI (Stage 2ème année)</t>
+  </si>
+  <si>
+    <t>Création et installation WSUS</t>
   </si>
 </sst>
 </file>
@@ -781,6 +768,10 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -818,10 +809,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1058,56 +1045,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="47" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="48"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:26" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="36" t="s">
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="38"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="40"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="32"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1119,22 +1106,22 @@
       </c>
     </row>
     <row r="5" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="33" t="s">
-        <v>49</v>
+      <c r="A5" s="35" t="s">
+        <v>36</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="37"/>
     </row>
     <row r="6" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="41" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1157,8 +1144,8 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="324.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="43"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="45"/>
+      <c r="B7" s="42"/>
       <c r="C7" s="7" t="s">
         <v>17</v>
       </c>
@@ -1197,16 +1184,16 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="40"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1228,21 +1215,21 @@
     </row>
     <row r="9" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="C9" s="24" t="s">
         <v>25</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>26</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="1"/>
@@ -1266,23 +1253,23 @@
     </row>
     <row r="10" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="1"/>
@@ -1306,23 +1293,23 @@
     </row>
     <row r="11" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="1"/>
@@ -1346,23 +1333,23 @@
     </row>
     <row r="12" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="1"/>
@@ -1386,23 +1373,23 @@
     </row>
     <row r="13" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="1"/>
@@ -1426,22 +1413,22 @@
     </row>
     <row r="14" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="E14" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1464,23 +1451,23 @@
     </row>
     <row r="15" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="1"/>
@@ -1504,26 +1491,26 @@
     </row>
     <row r="16" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="11"/>
       <c r="F16" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H16" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1583,14 +1570,14 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="31"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="32"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="34"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1611,16 +1598,16 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28" t="s">
-        <v>39</v>
+      <c r="A20" s="30" t="s">
+        <v>31</v>
       </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="30"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="32"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1642,20 +1629,20 @@
     </row>
     <row r="21" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G21" s="11"/>
       <c r="H21" s="13"/>
@@ -1680,21 +1667,21 @@
     </row>
     <row r="22" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="1"/>
@@ -1829,14 +1816,14 @@
       <c r="Z26" s="1"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="31"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="32"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="34"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -1857,16 +1844,16 @@
       <c r="Z27" s="1"/>
     </row>
     <row r="28" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28" t="s">
-        <v>43</v>
+      <c r="A28" s="30" t="s">
+        <v>33</v>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="30"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="32"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -1888,26 +1875,26 @@
     </row>
     <row r="29" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="11"/>
       <c r="F29" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -1930,20 +1917,20 @@
     </row>
     <row r="30" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="13"/>
@@ -1968,23 +1955,23 @@
     </row>
     <row r="31" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="16"/>
       <c r="F31" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="1"/>
